--- a/Data/IceStation2d/23aug2025coring_melt_ponds/20250823-PS149_46-1-SI_corer_9cm-020-FYI-T3-melt_pond-RHO-TXT.xlsx
+++ b/Data/IceStation2d/23aug2025coring_melt_ponds/20250823-PS149_46-1-SI_corer_9cm-020-FYI-T3-melt_pond-RHO-TXT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Contrasts coring\Data\IceStation2d\23aug2025coring_melt_ponds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6549ABF3-1737-4492-AEB5-9DC3BDE06EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A34D67-0577-42C4-8E00-35212C611428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata-core" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="334">
   <si>
     <t>Core</t>
   </si>
@@ -968,9 +968,6 @@
     <t>scatter layer</t>
   </si>
   <si>
-    <t>collected escaped brine from the core craddle and from the band saw table while cutting the core</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -1047,12 +1044,6 @@
   </si>
   <si>
     <t>Shimadzu balance UX4200H+SK101 specific gravity kit</t>
-  </si>
-  <si>
-    <t>g of brine</t>
-  </si>
-  <si>
-    <t>% of mass of brine that was recovered in the sleeve, core craddle and bandsaw table</t>
   </si>
   <si>
     <t>mark start 352 T3POND</t>
@@ -23436,7 +23427,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="143" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D1" s="143"/>
       <c r="E1" s="143"/>
@@ -23478,7 +23469,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="143" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
@@ -23546,7 +23537,7 @@
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
@@ -23615,10 +23606,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="B16" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -28109,7 +28100,7 @@
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="146" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="146"/>
       <c r="E4" s="146"/>
@@ -28278,7 +28269,7 @@
       <c r="E9" s="35"/>
       <c r="G9" s="34"/>
       <c r="I9" s="22" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
@@ -29011,13 +29002,13 @@
       <c r="B32" s="51"/>
       <c r="C32" s="48"/>
       <c r="D32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
@@ -29319,7 +29310,7 @@
     </row>
     <row r="42" spans="1:25" ht="63.75" customHeight="1">
       <c r="A42" s="151" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B42" s="151"/>
       <c r="C42" s="151"/>
@@ -29963,7 +29954,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E5" s="62">
         <v>0.5</v>
@@ -30001,7 +29992,7 @@
         <v>7.5000000000000011E-2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E6" s="62">
         <v>0.6</v>
@@ -30039,7 +30030,7 @@
         <v>0.125</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E7" s="62">
         <v>1.2</v>
@@ -30077,7 +30068,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E8" s="62">
         <v>1.8</v>
@@ -30115,7 +30106,7 @@
         <v>0.23500000000000001</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E9" s="62">
         <v>1.8</v>
@@ -30165,15 +30156,6 @@
       <c r="A11" s="141"/>
       <c r="B11" s="141"/>
       <c r="C11" s="142"/>
-      <c r="D11" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="E11" s="6">
-        <v>7.1</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>305</v>
-      </c>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
@@ -30194,13 +30176,7 @@
       <c r="B12" s="142"/>
       <c r="C12" s="142"/>
       <c r="E12" s="62"/>
-      <c r="N12" s="6">
-        <f>133-68</f>
-        <v>65</v>
-      </c>
-      <c r="O12" s="9" t="s">
-        <v>332</v>
-      </c>
+      <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -30220,13 +30196,7 @@
       <c r="B13" s="141"/>
       <c r="C13" s="142"/>
       <c r="E13" s="62"/>
-      <c r="N13" s="6">
-        <f>N12/(N12+686)</f>
-        <v>8.6551264980026632E-2</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>333</v>
-      </c>
+      <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -32284,7 +32254,7 @@
       <c r="D4" s="158"/>
       <c r="E4" s="158"/>
       <c r="F4" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
@@ -32366,7 +32336,7 @@
       <c r="D7" s="158"/>
       <c r="E7" s="158"/>
       <c r="F7" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
@@ -32399,7 +32369,7 @@
       <c r="D8" s="158"/>
       <c r="E8" s="158"/>
       <c r="F8" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
@@ -32432,7 +32402,7 @@
       <c r="D9" s="158"/>
       <c r="E9" s="158"/>
       <c r="F9" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
@@ -34611,7 +34581,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E4" s="6">
         <v>114.05</v>
@@ -34624,7 +34594,7 @@
         <v>0.85829102181192873</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -34653,19 +34623,19 @@
         <v>7.5000000000000011E-2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E5" s="6">
         <v>117.33</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G5" s="6">
         <v>0.83150000000000002</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -34694,7 +34664,7 @@
         <v>0.125</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E6" s="6">
         <v>126.19</v>
@@ -34707,7 +34677,7 @@
         <v>0.83881193540650734</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -34736,7 +34706,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E7" s="6">
         <v>141.09</v>
@@ -34749,7 +34719,7 @@
         <v>0.85036485213105251</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -34778,7 +34748,7 @@
         <v>0.23500000000000001</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E8" s="6">
         <v>187.43</v>
@@ -34791,7 +34761,7 @@
         <v>0.86635190950025021</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -34851,10 +34821,10 @@
       <c r="B11" s="142"/>
       <c r="C11" s="142"/>
       <c r="D11" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>315</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -34895,7 +34865,7 @@
       <c r="B13" s="142"/>
       <c r="C13" s="142"/>
       <c r="H13" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -34917,7 +34887,7 @@
       <c r="B14" s="141"/>
       <c r="C14" s="142"/>
       <c r="H14" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
@@ -35057,7 +35027,7 @@
       <c r="C21" s="142"/>
       <c r="D21" s="62"/>
       <c r="I21" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -35079,7 +35049,7 @@
       <c r="C22" s="142"/>
       <c r="D22" s="62"/>
       <c r="I22" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
